--- a/diseases/d091/2000-2004.xlsx
+++ b/diseases/d091/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -2397,9 +2388,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2941,9 +2929,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3485,9 +3470,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4029,9 +4011,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4573,9 +4552,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5117,9 +5093,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5661,9 +5634,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6205,9 +6175,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6749,9 +6716,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7293,9 +7257,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7837,9 +7798,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -10009,9 +9967,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10405,9 +10360,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10553,9 +10505,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11097,9 +11046,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11245,9 +11191,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -11789,9 +11732,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -11937,9 +11877,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -12481,9 +12418,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12629,9 +12563,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13173,9 +13104,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13321,9 +13249,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -13865,9 +13790,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14013,9 +13935,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -14557,9 +14476,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14705,9 +14621,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -15249,9 +15162,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -15397,9 +15307,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15941,9 +15848,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -16089,9 +15993,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -16633,9 +16534,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -16781,9 +16679,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17325,9 +17220,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17473,9 +17365,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -18017,9 +17906,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -18165,9 +18051,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -18709,9 +18592,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -19105,9 +18985,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -19253,9 +19130,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -19797,9 +19671,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -19945,9 +19816,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -20489,9 +20357,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20637,9 +20502,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -21181,9 +21043,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21329,9 +21188,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21873,9 +21729,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22021,9 +21874,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -22565,9 +22415,6 @@
       <c r="O127" t="n">
         <v>3</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -22713,9 +22560,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -23257,9 +23101,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -23405,9 +23246,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -23949,9 +23787,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -24097,9 +23932,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -24641,9 +24473,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -24789,9 +24618,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -25333,9 +25159,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -25481,9 +25304,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -26025,9 +25845,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -26173,9 +25990,6 @@
       <c r="O148" t="n">
         <v>2</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -26717,9 +26531,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -26865,9 +26676,6 @@
       <c r="O152" t="n">
         <v>4</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -27409,9 +27217,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -27805,9 +27610,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -27953,9 +27755,6 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -28497,9 +28296,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -28645,9 +28441,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -29189,9 +28982,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -29337,9 +29127,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -29881,9 +29668,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -30029,9 +29813,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -30573,9 +30354,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -30721,9 +30499,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -31265,9 +31040,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -31413,9 +31185,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -31957,9 +31726,6 @@
       <c r="O181" t="n">
         <v>1</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -32105,9 +31871,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -32649,9 +32412,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -32797,9 +32557,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -33341,9 +33098,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -33489,9 +33243,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -34033,9 +33784,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -34181,9 +33929,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -34725,9 +34470,6 @@
       <c r="O197" t="n">
         <v>3</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.006289693798941615</v>
       </c>
@@ -34873,9 +34615,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -35417,9 +35156,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -35563,9 +35299,6 @@
         <v>0</v>
       </c>
       <c r="O202" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q202" t="n">
         <v>0</v>
       </c>
       <c r="R202" t="n">
